--- a/results/sankeyData.xlsx
+++ b/results/sankeyData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="22752" uniqueCount="2184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="26862" uniqueCount="2188">
   <si>
     <t>ICIMD</t>
   </si>
@@ -6620,6 +6620,18 @@
   </si>
   <si>
     <t>HCP 24 [5.0] Global Platform 3 #9467bd</t>
+  </si>
+  <si>
+    <t>HCP 19 [6.0] Targeted Platform 3 #9467bd</t>
+  </si>
+  <si>
+    <t>HCP 19 [3.0] Targeted Platform 5 #9467bd</t>
+  </si>
+  <si>
+    <t>HCP 13 [19.0] Global Platform 5 #9467bd</t>
+  </si>
+  <si>
+    <t>HCP 8 [22.0] Global Platform 5 #9467bd</t>
   </si>
 </sst>
 </file>
@@ -6665,7 +6677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D120"/>
+  <dimension ref="A1:D122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42.85546875" customWidth="true"/>
@@ -6724,10 +6736,10 @@
         <v>12</v>
       </c>
       <c r="C4" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>2065</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="5">
@@ -6738,10 +6750,10 @@
         <v>13</v>
       </c>
       <c r="C5" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>2159</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="6">
@@ -6892,10 +6904,10 @@
         <v>24</v>
       </c>
       <c r="C16" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>2160</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="17">
@@ -7046,10 +7058,10 @@
         <v>12</v>
       </c>
       <c r="C27" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>1836</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="28">
@@ -7298,10 +7310,10 @@
         <v>31</v>
       </c>
       <c r="C45" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>1504</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="46">
@@ -7449,13 +7461,13 @@
         <v>759</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C56" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="57">
@@ -7463,13 +7475,13 @@
         <v>759</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C57" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>1508</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="58">
@@ -7477,13 +7489,13 @@
         <v>759</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C58" s="0">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="59">
@@ -7491,13 +7503,13 @@
         <v>759</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C59" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>789</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="60">
@@ -7505,13 +7517,13 @@
         <v>759</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C60" s="0">
         <v>3</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>1950</v>
+        <v>789</v>
       </c>
     </row>
     <row r="61">
@@ -7519,27 +7531,27 @@
         <v>759</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C61" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>791</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C62" s="0">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="63">
@@ -7547,13 +7559,13 @@
         <v>760</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C63" s="0">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="64">
@@ -7561,13 +7573,13 @@
         <v>760</v>
       </c>
       <c r="B64" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64" s="0">
         <v>12</v>
       </c>
-      <c r="C64" s="0">
-        <v>13</v>
-      </c>
       <c r="D64" s="0" t="s">
-        <v>2161</v>
+        <v>793</v>
       </c>
     </row>
     <row r="65">
@@ -7575,13 +7587,13 @@
         <v>760</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C65" s="0">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>1043</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="66">
@@ -7589,13 +7601,13 @@
         <v>760</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C66" s="0">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="67">
@@ -7603,13 +7615,13 @@
         <v>760</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C67" s="0">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>1951</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="68">
@@ -7617,13 +7629,13 @@
         <v>760</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C68" s="0">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="69">
@@ -7631,13 +7643,13 @@
         <v>760</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C69" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>1516</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="70">
@@ -7645,13 +7657,13 @@
         <v>760</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C70" s="0">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>2162</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="71">
@@ -7659,13 +7671,13 @@
         <v>760</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C71" s="0">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="72">
@@ -7673,13 +7685,13 @@
         <v>760</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C72" s="0">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="73">
@@ -7687,13 +7699,13 @@
         <v>760</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C73" s="0">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>1520</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="74">
@@ -7701,13 +7713,13 @@
         <v>760</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C74" s="0">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>1954</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="75">
@@ -7715,13 +7727,13 @@
         <v>760</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C75" s="0">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>2163</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="76">
@@ -7729,13 +7741,13 @@
         <v>760</v>
       </c>
       <c r="B76" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C76" s="0">
         <v>24</v>
       </c>
-      <c r="C76" s="0">
-        <v>12</v>
-      </c>
       <c r="D76" s="0" t="s">
-        <v>1523</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="77">
@@ -7743,13 +7755,13 @@
         <v>760</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C77" s="0">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>1849</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="78">
@@ -7757,13 +7769,13 @@
         <v>760</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C78" s="0">
         <v>15</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>1525</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="79">
@@ -7771,13 +7783,13 @@
         <v>760</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C79" s="0">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="80">
@@ -7785,13 +7797,13 @@
         <v>760</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C80" s="0">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>1527</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="81">
@@ -7799,13 +7811,13 @@
         <v>760</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C81" s="0">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="82">
@@ -7813,13 +7825,13 @@
         <v>760</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C82" s="0">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>1957</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="83">
@@ -7827,13 +7839,13 @@
         <v>760</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C83" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="84">
@@ -7841,27 +7853,27 @@
         <v>760</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C84" s="0">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="C85" s="0">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>1532</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="86">
@@ -7869,13 +7881,13 @@
         <v>761</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C86" s="0">
         <v>2</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>817</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="87">
@@ -7883,13 +7895,13 @@
         <v>761</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C87" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="88">
@@ -7897,13 +7909,13 @@
         <v>761</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C88" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="89">
@@ -7911,13 +7923,13 @@
         <v>761</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C89" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="90">
@@ -7925,13 +7937,13 @@
         <v>761</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C90" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>1533</v>
+        <v>820</v>
       </c>
     </row>
     <row r="91">
@@ -7939,13 +7951,13 @@
         <v>761</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C91" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>822</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="92">
@@ -7953,13 +7965,13 @@
         <v>761</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C92" s="0">
         <v>1</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="93">
@@ -7967,41 +7979,41 @@
         <v>761</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C93" s="0">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>1958</v>
+        <v>823</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="s">
-        <v>6</v>
+        <v>761</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C94" s="0">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>129</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="s">
-        <v>6</v>
+        <v>761</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C95" s="0">
         <v>1</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="96">
@@ -8009,13 +8021,13 @@
         <v>6</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C96" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>1535</v>
+        <v>129</v>
       </c>
     </row>
     <row r="97">
@@ -8023,13 +8035,13 @@
         <v>6</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C97" s="0">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>1959</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="98">
@@ -8037,13 +8049,13 @@
         <v>6</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C98" s="0">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>133</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="99">
@@ -8051,13 +8063,13 @@
         <v>6</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C99" s="0">
         <v>4</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="100">
@@ -8065,13 +8077,13 @@
         <v>6</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C100" s="0">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D100" s="0" t="s">
-        <v>1538</v>
+        <v>134</v>
       </c>
     </row>
     <row r="101">
@@ -8079,13 +8091,13 @@
         <v>6</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C101" s="0">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>1060</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="102">
@@ -8093,13 +8105,13 @@
         <v>6</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C102" s="0">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>2074</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="103">
@@ -8107,13 +8119,13 @@
         <v>6</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C103" s="0">
         <v>2</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>138</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="104">
@@ -8121,13 +8133,13 @@
         <v>6</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C104" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D104" s="0" t="s">
-        <v>1961</v>
+        <v>138</v>
       </c>
     </row>
     <row r="105">
@@ -8135,41 +8147,41 @@
         <v>6</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C105" s="0">
         <v>1</v>
       </c>
       <c r="D105" s="0" t="s">
-        <v>1541</v>
+        <v>139</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C106" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D106" s="0" t="s">
-        <v>1542</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C107" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D107" s="0" t="s">
-        <v>1962</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="108">
@@ -8177,13 +8189,13 @@
         <v>7</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C108" s="0">
         <v>2</v>
       </c>
       <c r="D108" s="0" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="109">
@@ -8191,13 +8203,13 @@
         <v>7</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C109" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D109" s="0" t="s">
-        <v>145</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="110">
@@ -8205,13 +8217,13 @@
         <v>7</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C110" s="0">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D110" s="0" t="s">
-        <v>831</v>
+        <v>144</v>
       </c>
     </row>
     <row r="111">
@@ -8219,13 +8231,13 @@
         <v>7</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C111" s="0">
         <v>1</v>
       </c>
       <c r="D111" s="0" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="112">
@@ -8233,41 +8245,41 @@
         <v>7</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C112" s="0">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D112" s="0" t="s">
-        <v>148</v>
+        <v>831</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C113" s="0">
         <v>1</v>
       </c>
       <c r="D113" s="0" t="s">
-        <v>1963</v>
+        <v>147</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C114" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D114" s="0" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="115">
@@ -8275,13 +8287,13 @@
         <v>8</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C115" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D115" s="0" t="s">
-        <v>1546</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="116">
@@ -8289,13 +8301,13 @@
         <v>8</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C116" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D116" s="0" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="117">
@@ -8303,13 +8315,13 @@
         <v>8</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C117" s="0">
         <v>2</v>
       </c>
       <c r="D117" s="0" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="118">
@@ -8317,13 +8329,13 @@
         <v>8</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C118" s="0">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D118" s="0" t="s">
-        <v>1548</v>
+        <v>153</v>
       </c>
     </row>
     <row r="119">
@@ -8331,13 +8343,13 @@
         <v>8</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C119" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D119" s="0" t="s">
-        <v>156</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="120">
@@ -8345,12 +8357,40 @@
         <v>8</v>
       </c>
       <c r="B120" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="C120" s="0">
+        <v>11</v>
+      </c>
+      <c r="D120" s="0" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B121" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C121" s="0">
+        <v>1</v>
+      </c>
+      <c r="D121" s="0" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B122" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="C120" s="0">
+      <c r="C122" s="0">
         <v>2</v>
       </c>
-      <c r="D120" s="0" t="s">
+      <c r="D122" s="0" t="s">
         <v>157</v>
       </c>
     </row>
@@ -8360,7 +8400,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D255"/>
+  <dimension ref="A1:D260"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.140625" customWidth="true"/>
@@ -8405,10 +8445,10 @@
         <v>160</v>
       </c>
       <c r="C3" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>1549</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="4">
@@ -8419,10 +8459,10 @@
         <v>160</v>
       </c>
       <c r="C4" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>1964</v>
+        <v>835</v>
       </c>
     </row>
     <row r="5">
@@ -8461,10 +8501,10 @@
         <v>161</v>
       </c>
       <c r="C7" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>1550</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="8">
@@ -8475,10 +8515,10 @@
         <v>161</v>
       </c>
       <c r="C8" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>837</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9">
@@ -8629,10 +8669,10 @@
         <v>160</v>
       </c>
       <c r="C19" s="0">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>2076</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="20">
@@ -8699,10 +8739,10 @@
         <v>161</v>
       </c>
       <c r="C24" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="25">
@@ -8713,10 +8753,10 @@
         <v>161</v>
       </c>
       <c r="C25" s="0">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>1561</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="26">
@@ -8724,13 +8764,13 @@
         <v>12</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C26" s="0">
         <v>3</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>2164</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="27">
@@ -8738,41 +8778,41 @@
         <v>12</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C27" s="0">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>1967</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C28" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C29" s="0">
         <v>4</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>2125</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="30">
@@ -8780,13 +8820,13 @@
         <v>13</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C30" s="0">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>2165</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="31">
@@ -8794,13 +8834,13 @@
         <v>13</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C31" s="0">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="32">
@@ -8808,13 +8848,13 @@
         <v>13</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C32" s="0">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="33">
@@ -8822,13 +8862,13 @@
         <v>13</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C33" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>1069</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="34">
@@ -8836,13 +8876,13 @@
         <v>13</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C34" s="0">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>2166</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="35">
@@ -8853,38 +8893,38 @@
         <v>161</v>
       </c>
       <c r="C35" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C36" s="0">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>849</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C37" s="0">
         <v>1</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>199</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="38">
@@ -8892,13 +8932,13 @@
         <v>14</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C38" s="0">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>2167</v>
+        <v>849</v>
       </c>
     </row>
     <row r="39">
@@ -8906,13 +8946,13 @@
         <v>14</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C39" s="0">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>1970</v>
+        <v>199</v>
       </c>
     </row>
     <row r="40">
@@ -8923,10 +8963,10 @@
         <v>160</v>
       </c>
       <c r="C40" s="0">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>1571</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="41">
@@ -8934,13 +8974,13 @@
         <v>14</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C41" s="0">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>2168</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="42">
@@ -8948,13 +8988,13 @@
         <v>14</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C42" s="0">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>1862</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="43">
@@ -8965,10 +9005,10 @@
         <v>161</v>
       </c>
       <c r="C43" s="0">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>1076</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="44">
@@ -9063,10 +9103,10 @@
         <v>160</v>
       </c>
       <c r="C50" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>858</v>
+        <v>210</v>
       </c>
     </row>
     <row r="51">
@@ -9119,10 +9159,10 @@
         <v>161</v>
       </c>
       <c r="C54" s="0">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>862</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="55">
@@ -9130,13 +9170,13 @@
         <v>15</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C55" s="0">
         <v>11</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>2083</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="56">
@@ -9147,24 +9187,24 @@
         <v>162</v>
       </c>
       <c r="C56" s="0">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>1577</v>
+        <v>217</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C57" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>217</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="58">
@@ -9172,13 +9212,13 @@
         <v>16</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C58" s="0">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>1395</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="59">
@@ -9192,7 +9232,7 @@
         <v>2</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>219</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="60">
@@ -9203,10 +9243,10 @@
         <v>160</v>
       </c>
       <c r="C60" s="0">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>1974</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="61">
@@ -9217,10 +9257,10 @@
         <v>160</v>
       </c>
       <c r="C61" s="0">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>1975</v>
+        <v>222</v>
       </c>
     </row>
     <row r="62">
@@ -9228,13 +9268,13 @@
         <v>16</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C62" s="0">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>2169</v>
+        <v>223</v>
       </c>
     </row>
     <row r="63">
@@ -9242,13 +9282,13 @@
         <v>16</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C63" s="0">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>223</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="64">
@@ -9262,21 +9302,21 @@
         <v>3</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>2170</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C65" s="0">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>1976</v>
+        <v>227</v>
       </c>
     </row>
     <row r="66">
@@ -9315,10 +9355,10 @@
         <v>160</v>
       </c>
       <c r="C68" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>1979</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="69">
@@ -9357,10 +9397,10 @@
         <v>161</v>
       </c>
       <c r="C71" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>1264</v>
+        <v>233</v>
       </c>
     </row>
     <row r="72">
@@ -9382,13 +9422,13 @@
         <v>17</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C73" s="0">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>1588</v>
+        <v>235</v>
       </c>
     </row>
     <row r="74">
@@ -9399,24 +9439,24 @@
         <v>162</v>
       </c>
       <c r="C74" s="0">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C75" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>240</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="76">
@@ -9427,10 +9467,10 @@
         <v>160</v>
       </c>
       <c r="C76" s="0">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>1981</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="77">
@@ -9438,13 +9478,13 @@
         <v>18</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C77" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>1982</v>
+        <v>240</v>
       </c>
     </row>
     <row r="78">
@@ -9452,13 +9492,13 @@
         <v>18</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C78" s="0">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="79">
@@ -9466,13 +9506,13 @@
         <v>18</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C79" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>244</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="80">
@@ -9483,10 +9523,10 @@
         <v>161</v>
       </c>
       <c r="C80" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>1266</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="81">
@@ -9494,13 +9534,13 @@
         <v>18</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C81" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>1983</v>
+        <v>244</v>
       </c>
     </row>
     <row r="82">
@@ -9508,41 +9548,41 @@
         <v>18</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C82" s="0">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>1595</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C83" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>873</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C84" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>249</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="85">
@@ -9550,13 +9590,13 @@
         <v>19</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C85" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>250</v>
+        <v>873</v>
       </c>
     </row>
     <row r="86">
@@ -9564,13 +9604,13 @@
         <v>19</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C86" s="0">
         <v>4</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>874</v>
+        <v>249</v>
       </c>
     </row>
     <row r="87">
@@ -9578,13 +9618,13 @@
         <v>19</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C87" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="88">
@@ -9595,10 +9635,10 @@
         <v>160</v>
       </c>
       <c r="C88" s="0">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>1596</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="89">
@@ -9609,10 +9649,10 @@
         <v>160</v>
       </c>
       <c r="C89" s="0">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>255</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="90">
@@ -9623,10 +9663,10 @@
         <v>160</v>
       </c>
       <c r="C90" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="91">
@@ -9637,10 +9677,10 @@
         <v>160</v>
       </c>
       <c r="C91" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>1985</v>
+        <v>256</v>
       </c>
     </row>
     <row r="92">
@@ -9654,7 +9694,7 @@
         <v>2</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>876</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="93">
@@ -9679,10 +9719,10 @@
         <v>161</v>
       </c>
       <c r="C94" s="0">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>2171</v>
+        <v>877</v>
       </c>
     </row>
     <row r="95">
@@ -9693,10 +9733,10 @@
         <v>161</v>
       </c>
       <c r="C95" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>261</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="96">
@@ -9710,7 +9750,7 @@
         <v>1</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>1098</v>
+        <v>262</v>
       </c>
     </row>
     <row r="97">
@@ -9749,10 +9789,10 @@
         <v>160</v>
       </c>
       <c r="C99" s="0">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>879</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="100">
@@ -9777,10 +9817,10 @@
         <v>161</v>
       </c>
       <c r="C101" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>1600</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="102">
@@ -9861,10 +9901,10 @@
         <v>160</v>
       </c>
       <c r="C107" s="0">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D107" s="0" t="s">
-        <v>1601</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="108">
@@ -9875,10 +9915,10 @@
         <v>160</v>
       </c>
       <c r="C108" s="0">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D108" s="0" t="s">
-        <v>1987</v>
+        <v>275</v>
       </c>
     </row>
     <row r="109">
@@ -9886,13 +9926,13 @@
         <v>21</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C109" s="0">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D109" s="0" t="s">
-        <v>277</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="110">
@@ -9900,13 +9940,13 @@
         <v>21</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C110" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D110" s="0" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="111">
@@ -9917,10 +9957,10 @@
         <v>161</v>
       </c>
       <c r="C111" s="0">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D111" s="0" t="s">
-        <v>1272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="112">
@@ -9931,10 +9971,10 @@
         <v>161</v>
       </c>
       <c r="C112" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D112" s="0" t="s">
-        <v>1101</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="113">
@@ -10071,10 +10111,10 @@
         <v>160</v>
       </c>
       <c r="C122" s="0">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D122" s="0" t="s">
-        <v>2172</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="123">
@@ -10127,10 +10167,10 @@
         <v>160</v>
       </c>
       <c r="C126" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D126" s="0" t="s">
-        <v>1609</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="127">
@@ -10211,10 +10251,10 @@
         <v>161</v>
       </c>
       <c r="C132" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D132" s="0" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="133">
@@ -10225,10 +10265,10 @@
         <v>161</v>
       </c>
       <c r="C133" s="0">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D133" s="0" t="s">
-        <v>300</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="134">
@@ -10239,10 +10279,10 @@
         <v>161</v>
       </c>
       <c r="C134" s="0">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D134" s="0" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="135">
@@ -10253,10 +10293,10 @@
         <v>161</v>
       </c>
       <c r="C135" s="0">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D135" s="0" t="s">
-        <v>1613</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="136">
@@ -10267,10 +10307,10 @@
         <v>161</v>
       </c>
       <c r="C136" s="0">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D136" s="0" t="s">
-        <v>1614</v>
+        <v>304</v>
       </c>
     </row>
     <row r="137">
@@ -10278,13 +10318,13 @@
         <v>22</v>
       </c>
       <c r="B137" s="0" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C137" s="0">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D137" s="0" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="138">
@@ -10295,10 +10335,10 @@
         <v>162</v>
       </c>
       <c r="C138" s="0">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D138" s="0" t="s">
-        <v>305</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="139">
@@ -10309,10 +10349,10 @@
         <v>162</v>
       </c>
       <c r="C139" s="0">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D139" s="0" t="s">
-        <v>1615</v>
+        <v>307</v>
       </c>
     </row>
     <row r="140">
@@ -10323,24 +10363,24 @@
         <v>162</v>
       </c>
       <c r="C140" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D140" s="0" t="s">
-        <v>307</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="B141" s="0" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C141" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D141" s="0" t="s">
-        <v>1616</v>
+        <v>309</v>
       </c>
     </row>
     <row r="142">
@@ -10351,10 +10391,10 @@
         <v>159</v>
       </c>
       <c r="C142" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D142" s="0" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="143">
@@ -10393,10 +10433,10 @@
         <v>161</v>
       </c>
       <c r="C145" s="0">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D145" s="0" t="s">
-        <v>2173</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="146">
@@ -10404,27 +10444,27 @@
         <v>33</v>
       </c>
       <c r="B146" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C146" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D146" s="0" t="s">
-        <v>1620</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B147" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C147" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D147" s="0" t="s">
-        <v>317</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="148">
@@ -10435,10 +10475,10 @@
         <v>160</v>
       </c>
       <c r="C148" s="0">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D148" s="0" t="s">
-        <v>1621</v>
+        <v>317</v>
       </c>
     </row>
     <row r="149">
@@ -10449,10 +10489,10 @@
         <v>160</v>
       </c>
       <c r="C149" s="0">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D149" s="0" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="150">
@@ -10463,10 +10503,10 @@
         <v>160</v>
       </c>
       <c r="C150" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D150" s="0" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="151">
@@ -10474,13 +10514,13 @@
         <v>23</v>
       </c>
       <c r="B151" s="0" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C151" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D151" s="0" t="s">
-        <v>321</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="152">
@@ -10488,13 +10528,13 @@
         <v>23</v>
       </c>
       <c r="B152" s="0" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C152" s="0">
         <v>3</v>
       </c>
       <c r="D152" s="0" t="s">
-        <v>1881</v>
+        <v>321</v>
       </c>
     </row>
     <row r="153">
@@ -10502,13 +10542,13 @@
         <v>23</v>
       </c>
       <c r="B153" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C153" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D153" s="0" t="s">
-        <v>323</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="154">
@@ -10519,10 +10559,10 @@
         <v>162</v>
       </c>
       <c r="C154" s="0">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D154" s="0" t="s">
-        <v>2174</v>
+        <v>323</v>
       </c>
     </row>
     <row r="155">
@@ -10533,10 +10573,10 @@
         <v>162</v>
       </c>
       <c r="C155" s="0">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D155" s="0" t="s">
-        <v>1625</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="156">
@@ -10547,10 +10587,10 @@
         <v>162</v>
       </c>
       <c r="C156" s="0">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D156" s="0" t="s">
-        <v>1115</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="157">
@@ -10561,24 +10601,24 @@
         <v>162</v>
       </c>
       <c r="C157" s="0">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D157" s="0" t="s">
-        <v>1626</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B158" s="0" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C158" s="0">
         <v>1</v>
       </c>
       <c r="D158" s="0" t="s">
-        <v>328</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="159">
@@ -10589,10 +10629,10 @@
         <v>160</v>
       </c>
       <c r="C159" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D159" s="0" t="s">
-        <v>2175</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="160">
@@ -10645,10 +10685,10 @@
         <v>160</v>
       </c>
       <c r="C163" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D163" s="0" t="s">
-        <v>333</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="164">
@@ -10687,10 +10727,10 @@
         <v>161</v>
       </c>
       <c r="C166" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D166" s="0" t="s">
-        <v>1630</v>
+        <v>336</v>
       </c>
     </row>
     <row r="167">
@@ -10701,10 +10741,10 @@
         <v>161</v>
       </c>
       <c r="C167" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D167" s="0" t="s">
-        <v>338</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="168">
@@ -10718,7 +10758,7 @@
         <v>1</v>
       </c>
       <c r="D168" s="0" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="169">
@@ -10726,27 +10766,27 @@
         <v>24</v>
       </c>
       <c r="B169" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C169" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D169" s="0" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B170" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C170" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D170" s="0" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="171">
@@ -10757,10 +10797,10 @@
         <v>160</v>
       </c>
       <c r="C171" s="0">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D171" s="0" t="s">
-        <v>1883</v>
+        <v>341</v>
       </c>
     </row>
     <row r="172">
@@ -10771,10 +10811,10 @@
         <v>160</v>
       </c>
       <c r="C172" s="0">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D172" s="0" t="s">
-        <v>1632</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="173">
@@ -10785,10 +10825,10 @@
         <v>160</v>
       </c>
       <c r="C173" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D173" s="0" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="174">
@@ -10799,10 +10839,10 @@
         <v>160</v>
       </c>
       <c r="C174" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D174" s="0" t="s">
-        <v>1995</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="175">
@@ -10810,13 +10850,13 @@
         <v>25</v>
       </c>
       <c r="B175" s="0" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C175" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D175" s="0" t="s">
-        <v>1634</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="176">
@@ -10827,10 +10867,10 @@
         <v>161</v>
       </c>
       <c r="C176" s="0">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D176" s="0" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="177">
@@ -10838,13 +10878,13 @@
         <v>25</v>
       </c>
       <c r="B177" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C177" s="0">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D177" s="0" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="178">
@@ -10855,10 +10895,10 @@
         <v>162</v>
       </c>
       <c r="C178" s="0">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D178" s="0" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="179">
@@ -10869,10 +10909,10 @@
         <v>162</v>
       </c>
       <c r="C179" s="0">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D179" s="0" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="180">
@@ -10883,24 +10923,24 @@
         <v>162</v>
       </c>
       <c r="C180" s="0">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D180" s="0" t="s">
-        <v>1886</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B181" s="0" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C181" s="0">
         <v>2</v>
       </c>
       <c r="D181" s="0" t="s">
-        <v>351</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="182">
@@ -10911,10 +10951,10 @@
         <v>159</v>
       </c>
       <c r="C182" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D182" s="0" t="s">
-        <v>1640</v>
+        <v>351</v>
       </c>
     </row>
     <row r="183">
@@ -10922,13 +10962,13 @@
         <v>26</v>
       </c>
       <c r="B183" s="0" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C183" s="0">
         <v>3</v>
       </c>
       <c r="D183" s="0" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="184">
@@ -10939,10 +10979,10 @@
         <v>160</v>
       </c>
       <c r="C184" s="0">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D184" s="0" t="s">
-        <v>903</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="185">
@@ -10953,10 +10993,10 @@
         <v>160</v>
       </c>
       <c r="C185" s="0">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D185" s="0" t="s">
-        <v>2134</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="186">
@@ -10967,10 +11007,10 @@
         <v>160</v>
       </c>
       <c r="C186" s="0">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D186" s="0" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="187">
@@ -10981,10 +11021,10 @@
         <v>160</v>
       </c>
       <c r="C187" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D187" s="0" t="s">
-        <v>1644</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="188">
@@ -10992,13 +11032,13 @@
         <v>26</v>
       </c>
       <c r="B188" s="0" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C188" s="0">
         <v>2</v>
       </c>
       <c r="D188" s="0" t="s">
-        <v>1645</v>
+        <v>357</v>
       </c>
     </row>
     <row r="189">
@@ -11006,13 +11046,13 @@
         <v>26</v>
       </c>
       <c r="B189" s="0" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C189" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D189" s="0" t="s">
-        <v>2176</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="190">
@@ -11026,7 +11066,7 @@
         <v>2</v>
       </c>
       <c r="D190" s="0" t="s">
-        <v>1129</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="191">
@@ -11037,10 +11077,10 @@
         <v>161</v>
       </c>
       <c r="C191" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D191" s="0" t="s">
-        <v>1646</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="192">
@@ -11048,55 +11088,55 @@
         <v>26</v>
       </c>
       <c r="B192" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C192" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D192" s="0" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B193" s="0" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C193" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D193" s="0" t="s">
-        <v>906</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B194" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C194" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D194" s="0" t="s">
-        <v>363</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B195" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C195" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D195" s="0" t="s">
-        <v>364</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="196">
@@ -11104,13 +11144,13 @@
         <v>27</v>
       </c>
       <c r="B196" s="0" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C196" s="0">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D196" s="0" t="s">
-        <v>1998</v>
+        <v>906</v>
       </c>
     </row>
     <row r="197">
@@ -11124,7 +11164,7 @@
         <v>1</v>
       </c>
       <c r="D197" s="0" t="s">
-        <v>1647</v>
+        <v>363</v>
       </c>
     </row>
     <row r="198">
@@ -11132,13 +11172,13 @@
         <v>27</v>
       </c>
       <c r="B198" s="0" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C198" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D198" s="0" t="s">
-        <v>367</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="199">
@@ -11146,13 +11186,13 @@
         <v>27</v>
       </c>
       <c r="B199" s="0" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C199" s="0">
         <v>1</v>
       </c>
       <c r="D199" s="0" t="s">
-        <v>368</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="200">
@@ -11160,13 +11200,13 @@
         <v>27</v>
       </c>
       <c r="B200" s="0" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C200" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D200" s="0" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="201">
@@ -11180,7 +11220,7 @@
         <v>1</v>
       </c>
       <c r="D201" s="0" t="s">
-        <v>1649</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="202">
@@ -11188,13 +11228,13 @@
         <v>27</v>
       </c>
       <c r="B202" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C202" s="0">
         <v>1</v>
       </c>
       <c r="D202" s="0" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="203">
@@ -11202,13 +11242,13 @@
         <v>27</v>
       </c>
       <c r="B203" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C203" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D203" s="0" t="s">
-        <v>1650</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="204">
@@ -11216,55 +11256,55 @@
         <v>27</v>
       </c>
       <c r="B204" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C204" s="0">
         <v>1</v>
       </c>
       <c r="D204" s="0" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B205" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C205" s="0">
         <v>1</v>
       </c>
       <c r="D205" s="0" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B206" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C206" s="0">
         <v>2</v>
       </c>
       <c r="D206" s="0" t="s">
-        <v>375</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B207" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C207" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D207" s="0" t="s">
-        <v>376</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="208">
@@ -11275,10 +11315,10 @@
         <v>160</v>
       </c>
       <c r="C208" s="0">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D208" s="0" t="s">
-        <v>1999</v>
+        <v>374</v>
       </c>
     </row>
     <row r="209">
@@ -11289,10 +11329,10 @@
         <v>160</v>
       </c>
       <c r="C209" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D209" s="0" t="s">
-        <v>378</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="210">
@@ -11303,10 +11343,10 @@
         <v>160</v>
       </c>
       <c r="C210" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D210" s="0" t="s">
-        <v>1134</v>
+        <v>376</v>
       </c>
     </row>
     <row r="211">
@@ -11314,13 +11354,13 @@
         <v>28</v>
       </c>
       <c r="B211" s="0" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C211" s="0">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D211" s="0" t="s">
-        <v>2000</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="212">
@@ -11328,83 +11368,83 @@
         <v>28</v>
       </c>
       <c r="B212" s="0" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C212" s="0">
         <v>3</v>
       </c>
       <c r="D212" s="0" t="s">
-        <v>1654</v>
+        <v>378</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B213" s="0" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C213" s="0">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D213" s="0" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B214" s="0" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C214" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D214" s="0" t="s">
-        <v>384</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B215" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C215" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D215" s="0" t="s">
-        <v>1655</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B216" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C216" s="0">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D216" s="0" t="s">
-        <v>386</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B217" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C217" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D217" s="0" t="s">
-        <v>387</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="218">
@@ -11412,13 +11452,13 @@
         <v>29</v>
       </c>
       <c r="B218" s="0" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C218" s="0">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D218" s="0" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="219">
@@ -11426,13 +11466,13 @@
         <v>29</v>
       </c>
       <c r="B219" s="0" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C219" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D219" s="0" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="220">
@@ -11440,13 +11480,13 @@
         <v>29</v>
       </c>
       <c r="B220" s="0" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C220" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D220" s="0" t="s">
-        <v>390</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="221">
@@ -11454,13 +11494,13 @@
         <v>29</v>
       </c>
       <c r="B221" s="0" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C221" s="0">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D221" s="0" t="s">
-        <v>2001</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="222">
@@ -11468,13 +11508,13 @@
         <v>29</v>
       </c>
       <c r="B222" s="0" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C222" s="0">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D222" s="0" t="s">
-        <v>1657</v>
+        <v>387</v>
       </c>
     </row>
     <row r="223">
@@ -11482,13 +11522,13 @@
         <v>29</v>
       </c>
       <c r="B223" s="0" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C223" s="0">
         <v>1</v>
       </c>
       <c r="D223" s="0" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="224">
@@ -11496,13 +11536,13 @@
         <v>29</v>
       </c>
       <c r="B224" s="0" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C224" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D224" s="0" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
     </row>
     <row r="225">
@@ -11510,13 +11550,13 @@
         <v>29</v>
       </c>
       <c r="B225" s="0" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C225" s="0">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D225" s="0" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
     </row>
     <row r="226">
@@ -11524,83 +11564,83 @@
         <v>29</v>
       </c>
       <c r="B226" s="0" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C226" s="0">
         <v>1</v>
       </c>
       <c r="D226" s="0" t="s">
-        <v>2003</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B227" s="0" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C227" s="0">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D227" s="0" t="s">
-        <v>1659</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B228" s="0" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C228" s="0">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D228" s="0" t="s">
-        <v>1660</v>
+        <v>393</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B229" s="0" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C229" s="0">
         <v>3</v>
       </c>
       <c r="D229" s="0" t="s">
-        <v>2004</v>
+        <v>394</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B230" s="0" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C230" s="0">
         <v>6</v>
       </c>
       <c r="D230" s="0" t="s">
-        <v>2005</v>
+        <v>395</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B231" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C231" s="0">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D231" s="0" t="s">
-        <v>2006</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="232">
@@ -11608,13 +11648,13 @@
         <v>30</v>
       </c>
       <c r="B232" s="0" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C232" s="0">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D232" s="0" t="s">
-        <v>2007</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="233">
@@ -11622,13 +11662,13 @@
         <v>30</v>
       </c>
       <c r="B233" s="0" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C233" s="0">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D233" s="0" t="s">
-        <v>1665</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="234">
@@ -11636,13 +11676,13 @@
         <v>30</v>
       </c>
       <c r="B234" s="0" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C234" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D234" s="0" t="s">
-        <v>1666</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="235">
@@ -11650,83 +11690,83 @@
         <v>30</v>
       </c>
       <c r="B235" s="0" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C235" s="0">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D235" s="0" t="s">
-        <v>2008</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B236" s="0" t="s">
         <v>160</v>
       </c>
       <c r="C236" s="0">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D236" s="0" t="s">
-        <v>1668</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B237" s="0" t="s">
         <v>160</v>
       </c>
       <c r="C237" s="0">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D237" s="0" t="s">
-        <v>1669</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B238" s="0" t="s">
         <v>160</v>
       </c>
       <c r="C238" s="0">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D238" s="0" t="s">
-        <v>1670</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B239" s="0" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C239" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D239" s="0" t="s">
-        <v>412</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B240" s="0" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C240" s="0">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D240" s="0" t="s">
-        <v>1671</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="241">
@@ -11734,13 +11774,13 @@
         <v>31</v>
       </c>
       <c r="B241" s="0" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C241" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D241" s="0" t="s">
-        <v>1672</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="242">
@@ -11748,13 +11788,13 @@
         <v>31</v>
       </c>
       <c r="B242" s="0" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C242" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D242" s="0" t="s">
-        <v>415</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="243">
@@ -11762,13 +11802,13 @@
         <v>31</v>
       </c>
       <c r="B243" s="0" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C243" s="0">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D243" s="0" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="244">
@@ -11776,13 +11816,13 @@
         <v>31</v>
       </c>
       <c r="B244" s="0" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C244" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D244" s="0" t="s">
-        <v>1674</v>
+        <v>412</v>
       </c>
     </row>
     <row r="245">
@@ -11790,69 +11830,69 @@
         <v>31</v>
       </c>
       <c r="B245" s="0" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C245" s="0">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D245" s="0" t="s">
-        <v>417</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B246" s="0" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C246" s="0">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D246" s="0" t="s">
-        <v>1675</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B247" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C247" s="0">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D247" s="0" t="s">
-        <v>1676</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B248" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C248" s="0">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D248" s="0" t="s">
-        <v>1677</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B249" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C249" s="0">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D249" s="0" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="250">
@@ -11860,13 +11900,13 @@
         <v>32</v>
       </c>
       <c r="B250" s="0" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C250" s="0">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D250" s="0" t="s">
-        <v>925</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="251">
@@ -11874,13 +11914,13 @@
         <v>32</v>
       </c>
       <c r="B251" s="0" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C251" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D251" s="0" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
     </row>
     <row r="252">
@@ -11888,13 +11928,13 @@
         <v>32</v>
       </c>
       <c r="B252" s="0" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C252" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D252" s="0" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="253">
@@ -11902,13 +11942,13 @@
         <v>32</v>
       </c>
       <c r="B253" s="0" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C253" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D253" s="0" t="s">
-        <v>1679</v>
+        <v>422</v>
       </c>
     </row>
     <row r="254">
@@ -11916,13 +11956,13 @@
         <v>32</v>
       </c>
       <c r="B254" s="0" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C254" s="0">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D254" s="0" t="s">
-        <v>1680</v>
+        <v>423</v>
       </c>
     </row>
     <row r="255">
@@ -11930,12 +11970,82 @@
         <v>32</v>
       </c>
       <c r="B255" s="0" t="s">
+        <v>160</v>
+      </c>
+      <c r="C255" s="0">
+        <v>13</v>
+      </c>
+      <c r="D255" s="0" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B256" s="0" t="s">
+        <v>163</v>
+      </c>
+      <c r="C256" s="0">
+        <v>2</v>
+      </c>
+      <c r="D256" s="0" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B257" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="C257" s="0">
+        <v>4</v>
+      </c>
+      <c r="D257" s="0" t="s">
+        <v>1678</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B258" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="C258" s="0">
+        <v>5</v>
+      </c>
+      <c r="D258" s="0" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B259" s="0" t="s">
         <v>162</v>
       </c>
-      <c r="C255" s="0">
+      <c r="C259" s="0">
+        <v>1</v>
+      </c>
+      <c r="D259" s="0" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B260" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="C260" s="0">
         <v>3</v>
       </c>
-      <c r="D255" s="0" t="s">
+      <c r="D260" s="0" t="s">
         <v>1900</v>
       </c>
     </row>
@@ -11945,7 +12055,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D297"/>
+  <dimension ref="A1:D302"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.140625" customWidth="true"/>
@@ -11990,10 +12100,10 @@
         <v>433</v>
       </c>
       <c r="C3" s="0">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>929</v>
+        <v>440</v>
       </c>
     </row>
     <row r="4">
@@ -12046,10 +12156,10 @@
         <v>435</v>
       </c>
       <c r="C7" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>443</v>
+        <v>930</v>
       </c>
     </row>
     <row r="8">
@@ -12074,10 +12184,10 @@
         <v>436</v>
       </c>
       <c r="C9" s="0">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>931</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -12102,24 +12212,24 @@
         <v>437</v>
       </c>
       <c r="C11" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C12" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="13">
@@ -12127,13 +12237,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C13" s="0">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>449</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="14">
@@ -12141,13 +12251,13 @@
         <v>11</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C14" s="0">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>1683</v>
+        <v>451</v>
       </c>
     </row>
     <row r="15">
@@ -12158,10 +12268,10 @@
         <v>436</v>
       </c>
       <c r="C15" s="0">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>451</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="16">
@@ -12172,10 +12282,10 @@
         <v>436</v>
       </c>
       <c r="C16" s="0">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>1684</v>
+        <v>453</v>
       </c>
     </row>
     <row r="17">
@@ -12183,27 +12293,27 @@
         <v>11</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C17" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="C18" s="0">
         <v>1</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>454</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="19">
@@ -12214,10 +12324,10 @@
         <v>433</v>
       </c>
       <c r="C19" s="0">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>2102</v>
+        <v>457</v>
       </c>
     </row>
     <row r="20">
@@ -12228,10 +12338,10 @@
         <v>433</v>
       </c>
       <c r="C20" s="0">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>457</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="21">
@@ -12242,10 +12352,10 @@
         <v>433</v>
       </c>
       <c r="C21" s="0">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>1686</v>
+        <v>459</v>
       </c>
     </row>
     <row r="22">
@@ -12253,13 +12363,13 @@
         <v>12</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C22" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>459</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="23">
@@ -12270,10 +12380,10 @@
         <v>434</v>
       </c>
       <c r="C23" s="0">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="24">
@@ -12281,13 +12391,13 @@
         <v>12</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C24" s="0">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>1688</v>
+        <v>462</v>
       </c>
     </row>
     <row r="25">
@@ -12298,10 +12408,10 @@
         <v>435</v>
       </c>
       <c r="C25" s="0">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="26">
@@ -12309,13 +12419,13 @@
         <v>12</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C26" s="0">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>1692</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="27">
@@ -12326,38 +12436,38 @@
         <v>436</v>
       </c>
       <c r="C27" s="0">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>1902</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C28" s="0">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>1694</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C29" s="0">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>2177</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="30">
@@ -12365,13 +12475,13 @@
         <v>13</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C30" s="0">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>2178</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="31">
@@ -12379,13 +12489,13 @@
         <v>13</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C31" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>1697</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="32">
@@ -12393,13 +12503,13 @@
         <v>13</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C32" s="0">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>1150</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="33">
@@ -12407,13 +12517,13 @@
         <v>13</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C33" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="34">
@@ -12421,13 +12531,13 @@
         <v>13</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C34" s="0">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>2148</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="35">
@@ -12435,13 +12545,13 @@
         <v>13</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C35" s="0">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>1700</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="36">
@@ -12452,38 +12562,38 @@
         <v>436</v>
       </c>
       <c r="C36" s="0">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>1701</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C37" s="0">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>476</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C38" s="0">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>2014</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="39">
@@ -12491,13 +12601,13 @@
         <v>14</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C39" s="0">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="40">
@@ -12505,13 +12615,13 @@
         <v>14</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C40" s="0">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="41">
@@ -12522,10 +12632,10 @@
         <v>433</v>
       </c>
       <c r="C41" s="0">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="42">
@@ -12536,10 +12646,10 @@
         <v>433</v>
       </c>
       <c r="C42" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>480</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="43">
@@ -12547,13 +12657,13 @@
         <v>14</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C43" s="0">
         <v>1</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="44">
@@ -12561,13 +12671,13 @@
         <v>14</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C44" s="0">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>1703</v>
+        <v>482</v>
       </c>
     </row>
     <row r="45">
@@ -12578,10 +12688,10 @@
         <v>435</v>
       </c>
       <c r="C45" s="0">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>946</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="46">
@@ -12589,13 +12699,13 @@
         <v>14</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C46" s="0">
         <v>1</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>485</v>
+        <v>946</v>
       </c>
     </row>
     <row r="47">
@@ -12606,10 +12716,10 @@
         <v>436</v>
       </c>
       <c r="C47" s="0">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>2017</v>
+        <v>485</v>
       </c>
     </row>
     <row r="48">
@@ -12620,10 +12730,10 @@
         <v>436</v>
       </c>
       <c r="C48" s="0">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>2018</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="49">
@@ -12634,10 +12744,10 @@
         <v>436</v>
       </c>
       <c r="C49" s="0">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>1705</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="50">
@@ -12645,13 +12755,13 @@
         <v>14</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C50" s="0">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>489</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="51">
@@ -12662,24 +12772,24 @@
         <v>437</v>
       </c>
       <c r="C51" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>1706</v>
+        <v>489</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C52" s="0">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>1707</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="53">
@@ -12687,13 +12797,13 @@
         <v>15</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="C53" s="0">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>2020</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="54">
@@ -12701,13 +12811,13 @@
         <v>15</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C54" s="0">
         <v>2</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>492</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="55">
@@ -12718,10 +12828,10 @@
         <v>433</v>
       </c>
       <c r="C55" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>2021</v>
+        <v>492</v>
       </c>
     </row>
     <row r="56">
@@ -12729,13 +12839,13 @@
         <v>15</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C56" s="0">
         <v>4</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>495</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="57">
@@ -12743,13 +12853,13 @@
         <v>15</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C57" s="0">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>1906</v>
+        <v>495</v>
       </c>
     </row>
     <row r="58">
@@ -12757,13 +12867,13 @@
         <v>15</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C58" s="0">
         <v>1</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>497</v>
+        <v>951</v>
       </c>
     </row>
     <row r="59">
@@ -12771,13 +12881,13 @@
         <v>15</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C59" s="0">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>2022</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="60">
@@ -12788,10 +12898,10 @@
         <v>436</v>
       </c>
       <c r="C60" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>2023</v>
+        <v>497</v>
       </c>
     </row>
     <row r="61">
@@ -12802,10 +12912,10 @@
         <v>436</v>
       </c>
       <c r="C61" s="0">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>499</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="62">
@@ -12813,13 +12923,13 @@
         <v>15</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C62" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>500</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="63">
@@ -12827,27 +12937,27 @@
         <v>15</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C63" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>1445</v>
+        <v>499</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C64" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="65">
@@ -12855,13 +12965,13 @@
         <v>16</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="C65" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>2024</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="66">
@@ -12869,13 +12979,13 @@
         <v>16</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C66" s="0">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>504</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="67">
@@ -12883,13 +12993,13 @@
         <v>16</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C67" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>2025</v>
+        <v>504</v>
       </c>
     </row>
     <row r="68">
@@ -12897,13 +13007,13 @@
         <v>16</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C68" s="0">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>1716</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="69">
@@ -12911,13 +13021,13 @@
         <v>16</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C69" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>2179</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="70">
@@ -12925,13 +13035,13 @@
         <v>16</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C70" s="0">
         <v>2</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>510</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="71">
@@ -12939,13 +13049,13 @@
         <v>16</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C71" s="0">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>2027</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="72">
@@ -12953,55 +13063,55 @@
         <v>16</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C72" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>512</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C73" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C74" s="0">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>515</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C75" s="0">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>961</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="76">
@@ -13009,13 +13119,13 @@
         <v>17</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C76" s="0">
         <v>1</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
     </row>
     <row r="77">
@@ -13023,13 +13133,13 @@
         <v>17</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C77" s="0">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>1720</v>
+        <v>515</v>
       </c>
     </row>
     <row r="78">
@@ -13037,13 +13147,13 @@
         <v>17</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C78" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>519</v>
+        <v>961</v>
       </c>
     </row>
     <row r="79">
@@ -13054,10 +13164,10 @@
         <v>435</v>
       </c>
       <c r="C79" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="80">
@@ -13065,13 +13175,13 @@
         <v>17</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C80" s="0">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>521</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="81">
@@ -13079,13 +13189,13 @@
         <v>17</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C81" s="0">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>1722</v>
+        <v>519</v>
       </c>
     </row>
     <row r="82">
@@ -13093,13 +13203,13 @@
         <v>17</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C82" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="83">
@@ -13107,55 +13217,55 @@
         <v>17</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C83" s="0">
         <v>1</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>1724</v>
+        <v>521</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C84" s="0">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>2029</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C85" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>1162</v>
+        <v>523</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C86" s="0">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>1727</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="87">
@@ -13163,13 +13273,13 @@
         <v>18</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="C87" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>528</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="88">
@@ -13177,13 +13287,13 @@
         <v>18</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C88" s="0">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>529</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="89">
@@ -13191,13 +13301,13 @@
         <v>18</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C89" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>2030</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="90">
@@ -13205,13 +13315,13 @@
         <v>18</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C90" s="0">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>2031</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="91">
@@ -13219,13 +13329,13 @@
         <v>18</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C91" s="0">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>2107</v>
+        <v>528</v>
       </c>
     </row>
     <row r="92">
@@ -13233,13 +13343,13 @@
         <v>18</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C92" s="0">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
     </row>
     <row r="93">
@@ -13247,13 +13357,13 @@
         <v>18</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C93" s="0">
         <v>4</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="94">
@@ -13261,13 +13371,13 @@
         <v>18</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C94" s="0">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>2033</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="95">
@@ -13275,69 +13385,69 @@
         <v>18</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C95" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>2034</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C96" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C97" s="0">
         <v>4</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>540</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C98" s="0">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>965</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C99" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>543</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="100">
@@ -13345,13 +13455,13 @@
         <v>19</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C100" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D100" s="0" t="s">
-        <v>1734</v>
+        <v>538</v>
       </c>
     </row>
     <row r="101">
@@ -13359,13 +13469,13 @@
         <v>19</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C101" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
     </row>
     <row r="102">
@@ -13373,13 +13483,13 @@
         <v>19</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C102" s="0">
         <v>2</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>547</v>
+        <v>965</v>
       </c>
     </row>
     <row r="103">
@@ -13387,13 +13497,13 @@
         <v>19</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C103" s="0">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
     </row>
     <row r="104">
@@ -13401,13 +13511,13 @@
         <v>19</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C104" s="0">
         <v>3</v>
       </c>
       <c r="D104" s="0" t="s">
-        <v>549</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="105">
@@ -13415,13 +13525,13 @@
         <v>19</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C105" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D105" s="0" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
     </row>
     <row r="106">
@@ -13429,13 +13539,13 @@
         <v>19</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C106" s="0">
         <v>2</v>
       </c>
       <c r="D106" s="0" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
     </row>
     <row r="107">
@@ -13443,13 +13553,13 @@
         <v>19</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C107" s="0">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D107" s="0" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="108">
@@ -13457,13 +13567,13 @@
         <v>19</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C108" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D108" s="0" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
     </row>
     <row r="109">
@@ -13471,13 +13581,13 @@
         <v>19</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C109" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D109" s="0" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
     </row>
     <row r="110">
@@ -13485,13 +13595,13 @@
         <v>19</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C110" s="0">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D110" s="0" t="s">
-        <v>1737</v>
+        <v>551</v>
       </c>
     </row>
     <row r="111">
@@ -13499,13 +13609,13 @@
         <v>19</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C111" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D111" s="0" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
     </row>
     <row r="112">
@@ -13513,13 +13623,13 @@
         <v>19</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C112" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D112" s="0" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
     </row>
     <row r="113">
@@ -13527,69 +13637,69 @@
         <v>19</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C113" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D113" s="0" t="s">
-        <v>1909</v>
+        <v>554</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C114" s="0">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D114" s="0" t="s">
-        <v>1739</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C115" s="0">
         <v>4</v>
       </c>
       <c r="D115" s="0" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C116" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D116" s="0" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C117" s="0">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D117" s="0" t="s">
-        <v>970</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="118">
@@ -13597,13 +13707,13 @@
         <v>20</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C118" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D118" s="0" t="s">
-        <v>564</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="119">
@@ -13611,55 +13721,55 @@
         <v>20</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C119" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D119" s="0" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C120" s="0">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D120" s="0" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C121" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D121" s="0" t="s">
-        <v>567</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C122" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D122" s="0" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
     </row>
     <row r="123">
@@ -13667,13 +13777,13 @@
         <v>21</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C123" s="0">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D123" s="0" t="s">
-        <v>1740</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="124">
@@ -13681,13 +13791,13 @@
         <v>21</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C124" s="0">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D124" s="0" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
     </row>
     <row r="125">
@@ -13695,13 +13805,13 @@
         <v>21</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C125" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D125" s="0" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
     </row>
     <row r="126">
@@ -13709,13 +13819,13 @@
         <v>21</v>
       </c>
       <c r="B126" s="0" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C126" s="0">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D126" s="0" t="s">
-        <v>1741</v>
+        <v>568</v>
       </c>
     </row>
     <row r="127">
@@ -13723,13 +13833,13 @@
         <v>21</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C127" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D127" s="0" t="s">
-        <v>2035</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="128">
@@ -13737,13 +13847,13 @@
         <v>21</v>
       </c>
       <c r="B128" s="0" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C128" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D128" s="0" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
     </row>
     <row r="129">
@@ -13751,13 +13861,13 @@
         <v>21</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C129" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D129" s="0" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
     </row>
     <row r="130">
@@ -13765,13 +13875,13 @@
         <v>21</v>
       </c>
       <c r="B130" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C130" s="0">
         <v>2</v>
       </c>
       <c r="D130" s="0" t="s">
-        <v>1743</v>
+        <v>972</v>
       </c>
     </row>
     <row r="131">
@@ -13779,13 +13889,13 @@
         <v>21</v>
       </c>
       <c r="B131" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C131" s="0">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D131" s="0" t="s">
-        <v>577</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="132">
@@ -13793,13 +13903,13 @@
         <v>21</v>
       </c>
       <c r="B132" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C132" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D132" s="0" t="s">
-        <v>578</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="133">
@@ -13810,10 +13920,10 @@
         <v>436</v>
       </c>
       <c r="C133" s="0">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D133" s="0" t="s">
-        <v>2036</v>
+        <v>574</v>
       </c>
     </row>
     <row r="134">
@@ -13821,83 +13931,83 @@
         <v>21</v>
       </c>
       <c r="B134" s="0" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C134" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D134" s="0" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B135" s="0" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C135" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D135" s="0" t="s">
-        <v>582</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B136" s="0" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C136" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D136" s="0" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B137" s="0" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C137" s="0">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D137" s="0" t="s">
-        <v>1745</v>
+        <v>578</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B138" s="0" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C138" s="0">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D138" s="0" t="s">
-        <v>585</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B139" s="0" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C139" s="0">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D139" s="0" t="s">
-        <v>1746</v>
+        <v>974</v>
       </c>
     </row>
     <row r="140">
@@ -13905,13 +14015,13 @@
         <v>22</v>
       </c>
       <c r="B140" s="0" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="C140" s="0">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D140" s="0" t="s">
-        <v>1747</v>
+        <v>582</v>
       </c>
     </row>
     <row r="141">
@@ -13919,13 +14029,13 @@
         <v>22</v>
       </c>
       <c r="B141" s="0" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C141" s="0">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D141" s="0" t="s">
-        <v>1748</v>
+        <v>583</v>
       </c>
     </row>
     <row r="142">
@@ -13933,13 +14043,13 @@
         <v>22</v>
       </c>
       <c r="B142" s="0" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C142" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D142" s="0" t="s">
-        <v>589</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="143">
@@ -13947,13 +14057,13 @@
         <v>22</v>
       </c>
       <c r="B143" s="0" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C143" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D143" s="0" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
     </row>
     <row r="144">
@@ -13961,13 +14071,13 @@
         <v>22</v>
       </c>
       <c r="B144" s="0" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C144" s="0">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D144" s="0" t="s">
-        <v>1749</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="145">
@@ -13975,13 +14085,13 @@
         <v>22</v>
       </c>
       <c r="B145" s="0" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C145" s="0">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D145" s="0" t="s">
-        <v>1750</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="146">
@@ -13989,13 +14099,13 @@
         <v>22</v>
       </c>
       <c r="B146" s="0" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C146" s="0">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D146" s="0" t="s">
-        <v>593</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="147">
@@ -14003,13 +14113,13 @@
         <v>22</v>
       </c>
       <c r="B147" s="0" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C147" s="0">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D147" s="0" t="s">
-        <v>1751</v>
+        <v>589</v>
       </c>
     </row>
     <row r="148">
@@ -14017,13 +14127,13 @@
         <v>22</v>
       </c>
       <c r="B148" s="0" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C148" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D148" s="0" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
     </row>
     <row r="149">
@@ -14031,13 +14141,13 @@
         <v>22</v>
       </c>
       <c r="B149" s="0" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C149" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D149" s="0" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="150">
@@ -14045,13 +14155,13 @@
         <v>22</v>
       </c>
       <c r="B150" s="0" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C150" s="0">
         <v>4</v>
       </c>
       <c r="D150" s="0" t="s">
-        <v>1753</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="151">
@@ -14059,13 +14169,13 @@
         <v>22</v>
       </c>
       <c r="B151" s="0" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C151" s="0">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D151" s="0" t="s">
-        <v>2037</v>
+        <v>593</v>
       </c>
     </row>
     <row r="152">
@@ -14073,13 +14183,13 @@
         <v>22</v>
       </c>
       <c r="B152" s="0" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C152" s="0">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D152" s="0" t="s">
-        <v>1755</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="153">
@@ -14087,13 +14197,13 @@
         <v>22</v>
       </c>
       <c r="B153" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C153" s="0">
         <v>1</v>
       </c>
       <c r="D153" s="0" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
     </row>
     <row r="154">
@@ -14101,13 +14211,13 @@
         <v>22</v>
       </c>
       <c r="B154" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C154" s="0">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D154" s="0" t="s">
-        <v>1756</v>
+        <v>596</v>
       </c>
     </row>
     <row r="155">
@@ -14115,13 +14225,13 @@
         <v>22</v>
       </c>
       <c r="B155" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C155" s="0">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D155" s="0" t="s">
-        <v>1757</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="156">
@@ -14129,13 +14239,13 @@
         <v>22</v>
       </c>
       <c r="B156" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C156" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D156" s="0" t="s">
-        <v>604</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="157">
@@ -14143,13 +14253,13 @@
         <v>22</v>
       </c>
       <c r="B157" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C157" s="0">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D157" s="0" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="158">
@@ -14157,13 +14267,13 @@
         <v>22</v>
       </c>
       <c r="B158" s="0" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C158" s="0">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D158" s="0" t="s">
-        <v>606</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="159">
@@ -14171,13 +14281,13 @@
         <v>22</v>
       </c>
       <c r="B159" s="0" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C159" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D159" s="0" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
     </row>
     <row r="160">
@@ -14185,167 +14295,167 @@
         <v>22</v>
       </c>
       <c r="B160" s="0" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C160" s="0">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="D160" s="0" t="s">
-        <v>1759</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B161" s="0" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C161" s="0">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D161" s="0" t="s">
-        <v>2041</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B162" s="0" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C162" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D162" s="0" t="s">
-        <v>1335</v>
+        <v>604</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B163" s="0" t="s">
         <v>436</v>
       </c>
       <c r="C163" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D163" s="0" t="s">
-        <v>2154</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B164" s="0" t="s">
         <v>437</v>
       </c>
       <c r="C164" s="0">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D164" s="0" t="s">
-        <v>1920</v>
+        <v>607</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B165" s="0" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C165" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D165" s="0" t="s">
-        <v>618</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B166" s="0" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C166" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D166" s="0" t="s">
-        <v>1763</v>
+        <v>611</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B167" s="0" t="s">
         <v>433</v>
       </c>
       <c r="C167" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D167" s="0" t="s">
-        <v>620</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B168" s="0" t="s">
         <v>435</v>
       </c>
       <c r="C168" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D168" s="0" t="s">
-        <v>2180</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B169" s="0" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C169" s="0">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D169" s="0" t="s">
-        <v>622</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B170" s="0" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C170" s="0">
         <v>1</v>
       </c>
       <c r="D170" s="0" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B171" s="0" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C171" s="0">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D171" s="0" t="s">
-        <v>624</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="172">
@@ -14353,13 +14463,13 @@
         <v>23</v>
       </c>
       <c r="B172" s="0" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C172" s="0">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="D172" s="0" t="s">
-        <v>1765</v>
+        <v>618</v>
       </c>
     </row>
     <row r="173">
@@ -14367,13 +14477,13 @@
         <v>23</v>
       </c>
       <c r="B173" s="0" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C173" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D173" s="0" t="s">
-        <v>1766</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="174">
@@ -14381,13 +14491,13 @@
         <v>23</v>
       </c>
       <c r="B174" s="0" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C174" s="0">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D174" s="0" t="s">
-        <v>1182</v>
+        <v>620</v>
       </c>
     </row>
     <row r="175">
@@ -14395,13 +14505,13 @@
         <v>23</v>
       </c>
       <c r="B175" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C175" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D175" s="0" t="s">
-        <v>1767</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="176">
@@ -14409,13 +14519,13 @@
         <v>23</v>
       </c>
       <c r="B176" s="0" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C176" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D176" s="0" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
     </row>
     <row r="177">
@@ -14423,13 +14533,13 @@
         <v>23</v>
       </c>
       <c r="B177" s="0" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C177" s="0">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D177" s="0" t="s">
-        <v>1922</v>
+        <v>623</v>
       </c>
     </row>
     <row r="178">
@@ -14437,13 +14547,13 @@
         <v>23</v>
       </c>
       <c r="B178" s="0" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C178" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D178" s="0" t="s">
-        <v>1769</v>
+        <v>624</v>
       </c>
     </row>
     <row r="179">
@@ -14451,111 +14561,111 @@
         <v>23</v>
       </c>
       <c r="B179" s="0" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C179" s="0">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="D179" s="0" t="s">
-        <v>631</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B180" s="0" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C180" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D180" s="0" t="s">
-        <v>633</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B181" s="0" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C181" s="0">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D181" s="0" t="s">
-        <v>2181</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B182" s="0" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C182" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D182" s="0" t="s">
-        <v>635</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B183" s="0" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C183" s="0">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D183" s="0" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B184" s="0" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C184" s="0">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D184" s="0" t="s">
-        <v>637</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B185" s="0" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C185" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D185" s="0" t="s">
-        <v>638</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B186" s="0" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C186" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D186" s="0" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
     </row>
     <row r="187">
@@ -14563,13 +14673,13 @@
         <v>24</v>
       </c>
       <c r="B187" s="0" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C187" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D187" s="0" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
     </row>
     <row r="188">
@@ -14577,13 +14687,13 @@
         <v>24</v>
       </c>
       <c r="B188" s="0" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C188" s="0">
         <v>3</v>
       </c>
       <c r="D188" s="0" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
     </row>
     <row r="189">
@@ -14591,13 +14701,13 @@
         <v>24</v>
       </c>
       <c r="B189" s="0" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C189" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D189" s="0" t="s">
-        <v>2182</v>
+        <v>636</v>
       </c>
     </row>
     <row r="190">
@@ -14605,13 +14715,13 @@
         <v>24</v>
       </c>
       <c r="B190" s="0" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C190" s="0">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D190" s="0" t="s">
-        <v>1771</v>
+        <v>637</v>
       </c>
     </row>
     <row r="191">
@@ -14619,13 +14729,13 @@
         <v>24</v>
       </c>
       <c r="B191" s="0" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C191" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D191" s="0" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
     </row>
     <row r="192">
@@ -14633,13 +14743,13 @@
         <v>24</v>
       </c>
       <c r="B192" s="0" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C192" s="0">
         <v>1</v>
       </c>
       <c r="D192" s="0" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
     </row>
     <row r="193">
@@ -14647,83 +14757,83 @@
         <v>24</v>
       </c>
       <c r="B193" s="0" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C193" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D193" s="0" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B194" s="0" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C194" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D194" s="0" t="s">
-        <v>2183</v>
+        <v>641</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B195" s="0" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C195" s="0">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D195" s="0" t="s">
-        <v>1773</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B196" s="0" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C196" s="0">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D196" s="0" t="s">
-        <v>2045</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B197" s="0" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C197" s="0">
         <v>2</v>
       </c>
       <c r="D197" s="0" t="s">
-        <v>1775</v>
+        <v>644</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B198" s="0" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C198" s="0">
         <v>2</v>
       </c>
       <c r="D198" s="0" t="s">
-        <v>1776</v>
+        <v>646</v>
       </c>
     </row>
     <row r="199">
@@ -14731,13 +14841,13 @@
         <v>25</v>
       </c>
       <c r="B199" s="0" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C199" s="0">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D199" s="0" t="s">
-        <v>2047</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="200">
@@ -14745,13 +14855,13 @@
         <v>25</v>
       </c>
       <c r="B200" s="0" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C200" s="0">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D200" s="0" t="s">
-        <v>1777</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="201">
@@ -14759,13 +14869,13 @@
         <v>25</v>
       </c>
       <c r="B201" s="0" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C201" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D201" s="0" t="s">
-        <v>1778</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="202">
@@ -14773,13 +14883,13 @@
         <v>25</v>
       </c>
       <c r="B202" s="0" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C202" s="0">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D202" s="0" t="s">
-        <v>1779</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="203">
@@ -14787,13 +14897,13 @@
         <v>25</v>
       </c>
       <c r="B203" s="0" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C203" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D203" s="0" t="s">
-        <v>1780</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="204">
@@ -14801,13 +14911,13 @@
         <v>25</v>
       </c>
       <c r="B204" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C204" s="0">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D204" s="0" t="s">
-        <v>2048</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="205">
@@ -14815,13 +14925,13 @@
         <v>25</v>
       </c>
       <c r="B205" s="0" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C205" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D205" s="0" t="s">
-        <v>660</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="206">
@@ -14829,13 +14939,13 @@
         <v>25</v>
       </c>
       <c r="B206" s="0" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C206" s="0">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D206" s="0" t="s">
-        <v>1781</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="207">
@@ -14843,97 +14953,97 @@
         <v>25</v>
       </c>
       <c r="B207" s="0" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C207" s="0">
         <v>4</v>
       </c>
       <c r="D207" s="0" t="s">
-        <v>1782</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B208" s="0" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C208" s="0">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D208" s="0" t="s">
-        <v>662</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B209" s="0" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C209" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D209" s="0" t="s">
-        <v>1783</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B210" s="0" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C210" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D210" s="0" t="s">
-        <v>664</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B211" s="0" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C211" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D211" s="0" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B212" s="0" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C212" s="0">
         <v>2</v>
       </c>
       <c r="D212" s="0" t="s">
-        <v>1784</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B213" s="0" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C213" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D213" s="0" t="s">
-        <v>998</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="214">
@@ -14941,13 +15051,13 @@
         <v>26</v>
       </c>
       <c r="B214" s="0" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C214" s="0">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D214" s="0" t="s">
-        <v>1785</v>
+        <v>662</v>
       </c>
     </row>
     <row r="215">
@@ -14955,13 +15065,13 @@
         <v>26</v>
       </c>
       <c r="B215" s="0" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C215" s="0">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D215" s="0" t="s">
-        <v>1786</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="216">
@@ -14969,13 +15079,13 @@
         <v>26</v>
       </c>
       <c r="B216" s="0" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C216" s="0">
         <v>3</v>
       </c>
       <c r="D216" s="0" t="s">
-        <v>1787</v>
+        <v>664</v>
       </c>
     </row>
     <row r="217">
@@ -14983,13 +15093,13 @@
         <v>26</v>
       </c>
       <c r="B217" s="0" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C217" s="0">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D217" s="0" t="s">
-        <v>1348</v>
+        <v>665</v>
       </c>
     </row>
     <row r="218">
@@ -14997,13 +15107,13 @@
         <v>26</v>
       </c>
       <c r="B218" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C218" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D218" s="0" t="s">
-        <v>1788</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="219">
@@ -15011,13 +15121,13 @@
         <v>26</v>
       </c>
       <c r="B219" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C219" s="0">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D219" s="0" t="s">
-        <v>1789</v>
+        <v>998</v>
       </c>
     </row>
     <row r="220">
@@ -15025,13 +15135,13 @@
         <v>26</v>
       </c>
       <c r="B220" s="0" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C220" s="0">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D220" s="0" t="s">
-        <v>1790</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="221">
@@ -15039,83 +15149,83 @@
         <v>26</v>
       </c>
       <c r="B221" s="0" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C221" s="0">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D221" s="0" t="s">
-        <v>1791</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B222" s="0" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C222" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D222" s="0" t="s">
-        <v>1000</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B223" s="0" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C223" s="0">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D223" s="0" t="s">
-        <v>679</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B224" s="0" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C224" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D224" s="0" t="s">
-        <v>680</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B225" s="0" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C225" s="0">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D225" s="0" t="s">
-        <v>1792</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B226" s="0" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C226" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D226" s="0" t="s">
-        <v>1793</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="227">
@@ -15123,13 +15233,13 @@
         <v>27</v>
       </c>
       <c r="B227" s="0" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C227" s="0">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D227" s="0" t="s">
-        <v>683</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="228">
@@ -15137,13 +15247,13 @@
         <v>27</v>
       </c>
       <c r="B228" s="0" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C228" s="0">
         <v>1</v>
       </c>
       <c r="D228" s="0" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
     </row>
     <row r="229">
@@ -15151,13 +15261,13 @@
         <v>27</v>
       </c>
       <c r="B229" s="0" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C229" s="0">
         <v>1</v>
       </c>
       <c r="D229" s="0" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
     </row>
     <row r="230">
@@ -15165,13 +15275,13 @@
         <v>27</v>
       </c>
       <c r="B230" s="0" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C230" s="0">
         <v>2</v>
       </c>
       <c r="D230" s="0" t="s">
-        <v>1794</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="231">
@@ -15179,13 +15289,13 @@
         <v>27</v>
       </c>
       <c r="B231" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C231" s="0">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D231" s="0" t="s">
-        <v>1002</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="232">
@@ -15193,13 +15303,13 @@
         <v>27</v>
       </c>
       <c r="B232" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C232" s="0">
         <v>5</v>
       </c>
       <c r="D232" s="0" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
     </row>
     <row r="233">
@@ -15207,13 +15317,13 @@
         <v>27</v>
       </c>
       <c r="B233" s="0" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C233" s="0">
         <v>1</v>
       </c>
       <c r="D233" s="0" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
     </row>
     <row r="234">
@@ -15221,83 +15331,83 @@
         <v>27</v>
       </c>
       <c r="B234" s="0" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C234" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D234" s="0" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B235" s="0" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C235" s="0">
         <v>1</v>
       </c>
       <c r="D235" s="0" t="s">
-        <v>692</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B236" s="0" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C236" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D236" s="0" t="s">
-        <v>693</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B237" s="0" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C237" s="0">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D237" s="0" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B238" s="0" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C238" s="0">
         <v>1</v>
       </c>
       <c r="D238" s="0" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B239" s="0" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C239" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D239" s="0" t="s">
-        <v>1795</v>
+        <v>690</v>
       </c>
     </row>
     <row r="240">
@@ -15305,13 +15415,13 @@
         <v>28</v>
       </c>
       <c r="B240" s="0" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C240" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D240" s="0" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
     </row>
     <row r="241">
@@ -15319,13 +15429,13 @@
         <v>28</v>
       </c>
       <c r="B241" s="0" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C241" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D241" s="0" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
     </row>
     <row r="242">
@@ -15333,13 +15443,13 @@
         <v>28</v>
       </c>
       <c r="B242" s="0" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C242" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D242" s="0" t="s">
-        <v>1796</v>
+        <v>694</v>
       </c>
     </row>
     <row r="243">
@@ -15347,13 +15457,13 @@
         <v>28</v>
       </c>
       <c r="B243" s="0" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C243" s="0">
         <v>1</v>
       </c>
       <c r="D243" s="0" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
     </row>
     <row r="244">
@@ -15361,13 +15471,13 @@
         <v>28</v>
       </c>
       <c r="B244" s="0" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C244" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D244" s="0" t="s">
-        <v>702</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="245">
@@ -15375,111 +15485,111 @@
         <v>28</v>
       </c>
       <c r="B245" s="0" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C245" s="0">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D245" s="0" t="s">
-        <v>1797</v>
+        <v>697</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B246" s="0" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="C246" s="0">
         <v>1</v>
       </c>
       <c r="D246" s="0" t="s">
-        <v>2052</v>
+        <v>698</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B247" s="0" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C247" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D247" s="0" t="s">
-        <v>1799</v>
+        <v>699</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B248" s="0" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C248" s="0">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D248" s="0" t="s">
-        <v>1800</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B249" s="0" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C249" s="0">
         <v>1</v>
       </c>
       <c r="D249" s="0" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B250" s="0" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C250" s="0">
         <v>1</v>
       </c>
       <c r="D250" s="0" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B251" s="0" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C251" s="0">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D251" s="0" t="s">
-        <v>710</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B252" s="0" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C252" s="0">
         <v>2</v>
       </c>
       <c r="D252" s="0" t="s">
-        <v>711</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="253">
@@ -15487,13 +15597,13 @@
         <v>29</v>
       </c>
       <c r="B253" s="0" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="C253" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D253" s="0" t="s">
-        <v>712</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="254">
@@ -15501,13 +15611,13 @@
         <v>29</v>
       </c>
       <c r="B254" s="0" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C254" s="0">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D254" s="0" t="s">
-        <v>713</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="255">
@@ -15515,13 +15625,13 @@
         <v>29</v>
       </c>
       <c r="B255" s="0" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C255" s="0">
         <v>1</v>
       </c>
       <c r="D255" s="0" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
     </row>
     <row r="256">
@@ -15529,13 +15639,13 @@
         <v>29</v>
       </c>
       <c r="B256" s="0" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C256" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D256" s="0" t="s">
-        <v>1203</v>
+        <v>709</v>
       </c>
     </row>
     <row r="257">
@@ -15543,13 +15653,13 @@
         <v>29</v>
       </c>
       <c r="B257" s="0" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C257" s="0">
         <v>1</v>
       </c>
       <c r="D257" s="0" t="s">
-        <v>2053</v>
+        <v>710</v>
       </c>
     </row>
     <row r="258">
@@ -15557,13 +15667,13 @@
         <v>29</v>
       </c>
       <c r="B258" s="0" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C258" s="0">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D258" s="0" t="s">
-        <v>1802</v>
+        <v>711</v>
       </c>
     </row>
     <row r="259">
@@ -15571,13 +15681,13 @@
         <v>29</v>
       </c>
       <c r="B259" s="0" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C259" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D259" s="0" t="s">
-        <v>2055</v>
+        <v>712</v>
       </c>
     </row>
     <row r="260">
@@ -15585,13 +15695,13 @@
         <v>29</v>
       </c>
       <c r="B260" s="0" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C260" s="0">
         <v>1</v>
       </c>
       <c r="D260" s="0" t="s">
-        <v>720</v>
+        <v>713</v>
       </c>
     </row>
     <row r="261">
@@ -15599,13 +15709,13 @@
         <v>29</v>
       </c>
       <c r="B261" s="0" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C261" s="0">
         <v>1</v>
       </c>
       <c r="D261" s="0" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
     </row>
     <row r="262">
@@ -15613,97 +15723,97 @@
         <v>29</v>
       </c>
       <c r="B262" s="0" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C262" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D262" s="0" t="s">
-        <v>2056</v>
+        <v>715</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B263" s="0" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C263" s="0">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D263" s="0" t="s">
-        <v>2057</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B264" s="0" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C264" s="0">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D264" s="0" t="s">
-        <v>724</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B265" s="0" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C265" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D265" s="0" t="s">
-        <v>2058</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B266" s="0" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C266" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D266" s="0" t="s">
-        <v>1807</v>
+        <v>720</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B267" s="0" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C267" s="0">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D267" s="0" t="s">
-        <v>1808</v>
+        <v>721</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B268" s="0" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C268" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D268" s="0" t="s">
-        <v>1809</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="269">
@@ -15711,13 +15821,13 @@
         <v>30</v>
       </c>
       <c r="B269" s="0" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C269" s="0">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D269" s="0" t="s">
-        <v>730</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="270">
@@ -15725,13 +15835,13 @@
         <v>30</v>
       </c>
       <c r="B270" s="0" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C270" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D270" s="0" t="s">
-        <v>1810</v>
+        <v>724</v>
       </c>
     </row>
     <row r="271">
@@ -15739,13 +15849,13 @@
         <v>30</v>
       </c>
       <c r="B271" s="0" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C271" s="0">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D271" s="0" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="272">
@@ -15753,13 +15863,13 @@
         <v>30</v>
       </c>
       <c r="B272" s="0" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C272" s="0">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D272" s="0" t="s">
-        <v>2060</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="273">
@@ -15767,13 +15877,13 @@
         <v>30</v>
       </c>
       <c r="B273" s="0" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C273" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D273" s="0" t="s">
-        <v>1813</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="274">
@@ -15781,13 +15891,13 @@
         <v>30</v>
       </c>
       <c r="B274" s="0" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C274" s="0">
         <v>3</v>
       </c>
       <c r="D274" s="0" t="s">
-        <v>2061</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="275">
@@ -15795,97 +15905,97 @@
         <v>30</v>
       </c>
       <c r="B275" s="0" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C275" s="0">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D275" s="0" t="s">
-        <v>2062</v>
+        <v>730</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B276" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C276" s="0">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D276" s="0" t="s">
-        <v>1815</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B277" s="0" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C277" s="0">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D277" s="0" t="s">
-        <v>1816</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B278" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C278" s="0">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D278" s="0" t="s">
-        <v>1817</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B279" s="0" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C279" s="0">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D279" s="0" t="s">
-        <v>2063</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B280" s="0" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C280" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D280" s="0" t="s">
-        <v>1014</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B281" s="0" t="s">
         <v>436</v>
       </c>
       <c r="C281" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D281" s="0" t="s">
-        <v>742</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="282">
@@ -15893,13 +16003,13 @@
         <v>31</v>
       </c>
       <c r="B282" s="0" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C282" s="0">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D282" s="0" t="s">
-        <v>1819</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="283">
@@ -15907,13 +16017,13 @@
         <v>31</v>
       </c>
       <c r="B283" s="0" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C283" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D283" s="0" t="s">
-        <v>1820</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="284">
@@ -15921,13 +16031,13 @@
         <v>31</v>
       </c>
       <c r="B284" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C284" s="0">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D284" s="0" t="s">
-        <v>1821</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="285">
@@ -15935,13 +16045,13 @@
         <v>31</v>
       </c>
       <c r="B285" s="0" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C285" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D285" s="0" t="s">
-        <v>1940</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="286">
@@ -15949,83 +16059,83 @@
         <v>31</v>
       </c>
       <c r="B286" s="0" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C286" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D286" s="0" t="s">
-        <v>1823</v>
+        <v>742</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B287" s="0" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C287" s="0">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D287" s="0" t="s">
-        <v>1824</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B288" s="0" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C288" s="0">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D288" s="0" t="s">
-        <v>750</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B289" s="0" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C289" s="0">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D289" s="0" t="s">
-        <v>1825</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B290" s="0" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C290" s="0">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D290" s="0" t="s">
-        <v>1826</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B291" s="0" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C291" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D291" s="0" t="s">
-        <v>752</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="292">
@@ -16033,13 +16143,13 @@
         <v>32</v>
       </c>
       <c r="B292" s="0" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C292" s="0">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D292" s="0" t="s">
-        <v>2064</v>
+        <v>747</v>
       </c>
     </row>
     <row r="293">
@@ -16047,13 +16157,13 @@
         <v>32</v>
       </c>
       <c r="B293" s="0" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C293" s="0">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D293" s="0" t="s">
-        <v>1828</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="294">
@@ -16061,13 +16171,13 @@
         <v>32</v>
       </c>
       <c r="B294" s="0" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C294" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D294" s="0" t="s">
-        <v>1829</v>
+        <v>750</v>
       </c>
     </row>
     <row r="295">
@@ -16075,13 +16185,13 @@
         <v>32</v>
       </c>
       <c r="B295" s="0" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C295" s="0">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D295" s="0" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="296">
@@ -16089,13 +16199,13 @@
         <v>32</v>
       </c>
       <c r="B296" s="0" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C296" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D296" s="0" t="s">
-        <v>1831</v>
+        <v>752</v>
       </c>
     </row>
     <row r="297">
@@ -16103,12 +16213,82 @@
         <v>32</v>
       </c>
       <c r="B297" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="C297" s="0">
+        <v>13</v>
+      </c>
+      <c r="D297" s="0" t="s">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B298" s="0" t="s">
         <v>436</v>
       </c>
-      <c r="C297" s="0">
+      <c r="C298" s="0">
+        <v>1</v>
+      </c>
+      <c r="D298" s="0" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B299" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C299" s="0">
+        <v>2</v>
+      </c>
+      <c r="D299" s="0" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B300" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C300" s="0">
+        <v>10</v>
+      </c>
+      <c r="D300" s="0" t="s">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B301" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C301" s="0">
+        <v>1</v>
+      </c>
+      <c r="D301" s="0" t="s">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B302" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C302" s="0">
         <v>3</v>
       </c>
-      <c r="D297" s="0" t="s">
+      <c r="D302" s="0" t="s">
         <v>1832</v>
       </c>
     </row>
